--- a/data/trans_dic/IP25A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,14 +519,13 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -535,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -573,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -629,14 +611,11 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -646,62 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>39,85%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>32,21%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -714,69 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,07; 33,6</t>
+          <t>16,96; 37,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 46,27</t>
+          <t>30,33; 51,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 35,98</t>
+          <t>20,25; 41,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 23,75</t>
+          <t>27,49; 49,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,01; 43,93</t>
+          <t>35,51; 57,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,3; 52,69</t>
+          <t>31,48; 53,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,85; 48,48</t>
+          <t>25,19; 41,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,8; 25,26</t>
+          <t>35,76; 51,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,31; 36,25</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>32,55; 47,37</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25,28; 39,61</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10,3; 21,88</t>
+          <t>29,36; 45,25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -786,62 +735,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>44,44%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -854,69 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,09; 42,05</t>
+          <t>30,7; 47,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,59; 35,46</t>
+          <t>25,13; 41,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,94; 52,59</t>
+          <t>40,18; 56,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 28,14</t>
+          <t>31,89; 47,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,78; 42,68</t>
+          <t>29,58; 45,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,56; 41,43</t>
+          <t>38,27; 55,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,15; 53,1</t>
+          <t>33,94; 45,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 26,5</t>
+          <t>29,71; 40,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,41; 39,66</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>25,23; 35,84</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>38,9; 49,47</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,03; 25,48</t>
+          <t>41,11; 52,45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -926,62 +845,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35,38%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -994,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,96; 54,75</t>
+          <t>37,3; 59,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 21,13</t>
+          <t>8,53; 25,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,22; 44,53</t>
+          <t>29,36; 51,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 15,23</t>
+          <t>30,94; 50,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,82; 45,98</t>
+          <t>20,88; 38,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,47; 38,27</t>
+          <t>32,78; 55,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,49; 46,8</t>
+          <t>36,84; 51,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 12,02</t>
+          <t>17,1; 29,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,59; 47,17</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>15,51; 27,33</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>28,91; 43,02</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3,51; 10,94</t>
+          <t>33,9; 50,51</t>
         </is>
       </c>
     </row>
@@ -1066,62 +955,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>33,49%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,3%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -1134,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 34,13</t>
+          <t>19,31; 36,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,27; 47,51</t>
+          <t>33,63; 52,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,94; 40,92</t>
+          <t>26,48; 46,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 23,28</t>
+          <t>27,8; 46,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,71; 42,34</t>
+          <t>23,59; 41,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,29; 38,84</t>
+          <t>24,94; 44,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,68; 41,13</t>
+          <t>25,75; 38,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 31,33</t>
+          <t>30,17; 43,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,92; 35,43</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>27,41; 39,43</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>25,11; 38,13</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>10,87; 23,94</t>
+          <t>28,68; 41,71</t>
         </is>
       </c>
     </row>
@@ -1206,62 +1065,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>36,21%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>47,15%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -1274,69 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 39,07</t>
+          <t>19,58; 46,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,4; 37,78</t>
+          <t>16,3; 39,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,02; 63,83</t>
+          <t>44,45; 71,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,32</t>
+          <t>27,75; 54,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,65; 45,03</t>
+          <t>35,65; 60,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,15; 58,71</t>
+          <t>37,23; 63,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,08; 54,91</t>
+          <t>27,34; 45,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 25,94</t>
+          <t>29,92; 47,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,8; 38,27</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>27,85; 45,12</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>38,27; 56,06</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,07; 14,33</t>
+          <t>43,9; 62,66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1346,62 +1175,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>22,41%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>46,39%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
+          <t>50,46%</t>
         </is>
       </c>
     </row>
@@ -1414,69 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,29; 54,55</t>
+          <t>37,85; 59,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,42; 32,9</t>
+          <t>15,57; 36,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,01; 54,29</t>
+          <t>35,01; 58,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 32,29</t>
+          <t>35,18; 56,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,41; 52,62</t>
+          <t>14,91; 35,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,17; 31,87</t>
+          <t>41,68; 65,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,03; 62,29</t>
+          <t>39,56; 54,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,39; 23,44</t>
+          <t>17,14; 32,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35,42; 50,08</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>16,58; 30,16</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>39,0; 54,26</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>12,4; 23,94</t>
+          <t>41,8; 57,91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1486,62 +1285,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>23,74%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42,47%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -1554,62 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,49; 49,49</t>
+          <t>38,4; 53,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,59; 30,59</t>
+          <t>22,44; 36,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,83; 50,06</t>
+          <t>39,91; 54,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,93; 30,23</t>
+          <t>36,28; 50,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,18; 46,13</t>
+          <t>19,79; 32,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,73; 28,77</t>
+          <t>38,32; 53,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,66; 48,46</t>
+          <t>39,3; 49,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,85; 22,9</t>
+          <t>23,15; 32,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35,29; 45,13</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19,7; 28,51</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>37,84; 47,42</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>15,17; 24,74</t>
+          <t>42,33; 52,35</t>
         </is>
       </c>
     </row>
@@ -1626,62 +1395,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44,2%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>41,59%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -1694,62 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,62; 29,54</t>
+          <t>20,38; 31,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,98; 53,22</t>
+          <t>46,0; 59,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34,2; 46,52</t>
+          <t>40,52; 53,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,64</t>
+          <t>22,53; 34,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,28; 29,94</t>
+          <t>39,07; 52,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,85; 48,21</t>
+          <t>40,44; 53,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,72; 49,04</t>
+          <t>23,17; 32,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,43</t>
+          <t>44,53; 53,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,39; 27,92</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>39,92; 49,0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>36,97; 45,75</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,46; 6,38</t>
+          <t>42,71; 51,62</t>
         </is>
       </c>
     </row>
@@ -1766,62 +1505,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>40,44%</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -1834,62 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29,9; 35,54</t>
+          <t>33,28; 39,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,65; 34,63</t>
+          <t>32,47; 39,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36,76; 42,71</t>
+          <t>41,56; 48,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,79; 16,25</t>
+          <t>35,01; 41,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,65; 36,39</t>
+          <t>33,47; 39,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,91; 35,73</t>
+          <t>42,34; 48,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,47; 44,47</t>
+          <t>35,01; 39,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,65; 16,14</t>
+          <t>33,91; 38,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31,16; 35,08</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>30,31; 34,21</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>38,1; 42,5</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>12,08; 15,71</t>
+          <t>42,89; 47,56</t>
         </is>
       </c>
     </row>
@@ -1902,20 +1611,1627 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21371</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14904</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20382</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27340</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24339</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32519</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>48711</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>39243</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>7671; 16949</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16234; 27500</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9722; 19900</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14661; 26534</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>20966; 33958</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>17974; 30617</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>24824; 40920</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>40254; 57799</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>30866; 47564</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>34439</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29261</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46523</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37733</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>36731</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>48675</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72171</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>65992</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>95198</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>27269; 41950</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22365; 37270</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38592; 54256</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>30509; 45614</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>29154; 44709</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>40453; 58458</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>62616; 83813</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>55727; 76212</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>82951; 105839</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>30208</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9193</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22915</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25991</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20213</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25461</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>56198</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>29406</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>48376</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>23116; 36699</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5340; 15810</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16489; 29167</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20398; 33326</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>14020; 25959</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>19281; 32488</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>47120; 66107</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>22198; 38525</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>38987; 58076</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>18796</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29617</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24096</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>26292</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23963</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>26017</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45088</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>53580</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>50113</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13525; 25315</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>23436; 36706</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17963; 31259</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>20203; 33604</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17513; 30995</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>19036; 33719</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>36745; 54905</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>43427; 63233</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>41348; 60130</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>10813</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11205</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22293</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14018</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>21622</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20042</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>24832</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>32827</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>42335</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>6654; 15788</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6820; 16547</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>17186; 27449</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9718; 19076</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15888; 27060</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>14900; 25525</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>18867; 31233</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>25851; 40907</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>34538; 49300</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>25080</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12398</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>22649</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>24833</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13652</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>29310</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>49913</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>26050</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>51959</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>19715; 31205</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>7926; 18494</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>17057; 28307</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>19016; 30523</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>8269; 19583</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>22615; 35685</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>41991; 57976</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>18241; 34234</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>43042; 59632</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>54135</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>33721</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>59803</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>52326</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>33816</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>59725</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>106461</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>67537</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>119528</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>45728; 63150</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26355; 42930</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>50332; 68322</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>43274; 60078</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>25576; 42119</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>49281; 68946</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>93675; 117858</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>57120; 80009</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>107825; 133351</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>37458</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>77633</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>65852</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>39896</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>70891</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>73493</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>77354</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>148524</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>139344</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>29059; 45253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>67589; 87219</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>57047; 75788</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>30641; 47587</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>60462; 80565</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>62358; 83246</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>64544; 89279</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>134342; 161892</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>125981; 152271</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>223065</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>224398</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>279034</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>464536</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>472627</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>586097</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>204283; 241902</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>205233; 246614</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>258655; 300004</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>221272; 262514</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>228621; 267905</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>285822; 328199</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>436116; 490173</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>445925; 503374</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>556494; 617007</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP25A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,96; 37,48</t>
+          <t>18,19; 39,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,33; 51,38</t>
+          <t>29,17; 51,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,25; 41,44</t>
+          <t>20,92; 41,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,49; 49,76</t>
+          <t>28,0; 49,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,51; 57,51</t>
+          <t>35,63; 57,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,48; 53,62</t>
+          <t>31,38; 53,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,19; 41,53</t>
+          <t>25,38; 40,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,76; 51,34</t>
+          <t>35,38; 51,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,36; 45,25</t>
+          <t>29,71; 45,44</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,7; 47,23</t>
+          <t>31,18; 48,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,13; 41,87</t>
+          <t>25,41; 41,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,18; 56,48</t>
+          <t>39,84; 56,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,89; 47,68</t>
+          <t>32,02; 48,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,58; 45,36</t>
+          <t>29,28; 45,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,27; 55,3</t>
+          <t>39,09; 54,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,94; 45,43</t>
+          <t>33,69; 45,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,71; 40,63</t>
+          <t>29,95; 41,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,11; 52,45</t>
+          <t>41,57; 53,05</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,3; 59,22</t>
+          <t>38,11; 58,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 25,24</t>
+          <t>7,52; 22,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,36; 51,93</t>
+          <t>29,72; 52,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,94; 50,55</t>
+          <t>30,01; 48,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,88; 38,65</t>
+          <t>21,85; 39,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,78; 55,23</t>
+          <t>33,39; 53,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,84; 51,69</t>
+          <t>37,36; 51,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,1; 29,68</t>
+          <t>16,88; 28,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,9; 50,51</t>
+          <t>34,24; 49,44</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,31; 36,15</t>
+          <t>19,88; 36,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,63; 52,67</t>
+          <t>33,19; 52,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,48; 46,09</t>
+          <t>25,86; 45,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,8; 46,24</t>
+          <t>27,46; 45,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,59; 41,76</t>
+          <t>23,68; 42,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,94; 44,17</t>
+          <t>25,72; 44,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,75; 38,47</t>
+          <t>26,18; 38,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,17; 43,94</t>
+          <t>30,84; 44,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,68; 41,71</t>
+          <t>28,46; 41,83</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,58; 46,46</t>
+          <t>19,22; 45,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,3; 39,55</t>
+          <t>17,61; 41,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44,45; 71,0</t>
+          <t>43,69; 69,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,75; 54,47</t>
+          <t>26,39; 54,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,65; 60,71</t>
+          <t>35,76; 61,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,23; 63,78</t>
+          <t>36,98; 62,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,34; 45,26</t>
+          <t>26,61; 44,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,92; 47,34</t>
+          <t>29,66; 47,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,9; 62,66</t>
+          <t>44,56; 62,84</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,85; 59,91</t>
+          <t>36,27; 58,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,57; 36,32</t>
+          <t>15,08; 35,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,01; 58,1</t>
+          <t>34,56; 57,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,18; 56,46</t>
+          <t>34,27; 55,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,91; 35,3</t>
+          <t>16,12; 35,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,68; 65,77</t>
+          <t>41,9; 66,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,56; 54,62</t>
+          <t>40,1; 54,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,14; 32,18</t>
+          <t>17,76; 31,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,8; 57,91</t>
+          <t>42,1; 58,23</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,4; 53,04</t>
+          <t>37,43; 52,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,44; 36,55</t>
+          <t>22,19; 36,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,91; 54,17</t>
+          <t>40,26; 54,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,28; 50,37</t>
+          <t>36,28; 51,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,79; 32,59</t>
+          <t>19,91; 33,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,32; 53,61</t>
+          <t>39,75; 54,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,3; 49,45</t>
+          <t>39,23; 50,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,15; 32,43</t>
+          <t>22,82; 32,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,33; 52,35</t>
+          <t>42,15; 52,14</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,38; 31,74</t>
+          <t>20,81; 32,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46,0; 59,36</t>
+          <t>46,44; 59,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40,52; 53,83</t>
+          <t>39,85; 53,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,53; 34,99</t>
+          <t>23,0; 36,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,07; 52,06</t>
+          <t>39,25; 52,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,44; 53,98</t>
+          <t>40,93; 53,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,17; 32,05</t>
+          <t>23,53; 32,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,53; 53,67</t>
+          <t>44,19; 53,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,71; 51,62</t>
+          <t>42,76; 52,1</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33,28; 39,41</t>
+          <t>33,1; 39,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32,47; 39,02</t>
+          <t>32,37; 38,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41,56; 48,2</t>
+          <t>41,77; 48,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35,01; 41,54</t>
+          <t>34,95; 41,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,47; 39,22</t>
+          <t>33,46; 39,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,34; 48,62</t>
+          <t>42,2; 48,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,01; 39,35</t>
+          <t>35,17; 39,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>33,91; 38,28</t>
+          <t>33,72; 37,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42,89; 47,56</t>
+          <t>43,1; 47,51</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7671; 16949</t>
+          <t>8225; 17675</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16234; 27500</t>
+          <t>15611; 27428</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9722; 19900</t>
+          <t>10044; 20124</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14661; 26534</t>
+          <t>14932; 26566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20966; 33958</t>
+          <t>21038; 33712</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17974; 30617</t>
+          <t>17915; 30735</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24824; 40920</t>
+          <t>25014; 40185</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40254; 57799</t>
+          <t>39827; 57741</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30866; 47564</t>
+          <t>31226; 47764</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27269; 41950</t>
+          <t>27691; 42925</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22365; 37270</t>
+          <t>22614; 36803</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38592; 54256</t>
+          <t>38268; 54274</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30509; 45614</t>
+          <t>30632; 46654</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29154; 44709</t>
+          <t>28857; 45059</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40453; 58458</t>
+          <t>41326; 57576</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62616; 83813</t>
+          <t>62158; 84152</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55727; 76212</t>
+          <t>56175; 76943</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82951; 105839</t>
+          <t>83887; 107038</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23116; 36699</t>
+          <t>23620; 36555</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5340; 15810</t>
+          <t>4711; 14342</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16489; 29167</t>
+          <t>16694; 29347</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20398; 33326</t>
+          <t>19787; 32172</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14020; 25959</t>
+          <t>14673; 26447</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19281; 32488</t>
+          <t>19641; 31759</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47120; 66107</t>
+          <t>47785; 65838</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22198; 38525</t>
+          <t>21904; 37518</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38987; 58076</t>
+          <t>39372; 56848</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13525; 25315</t>
+          <t>13922; 25704</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23436; 36706</t>
+          <t>23131; 36621</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17963; 31259</t>
+          <t>17541; 30950</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20203; 33604</t>
+          <t>19956; 32908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17513; 30995</t>
+          <t>17576; 31364</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19036; 33719</t>
+          <t>19635; 33678</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36745; 54905</t>
+          <t>37365; 54834</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43427; 63233</t>
+          <t>44379; 63778</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41348; 60130</t>
+          <t>41030; 60310</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6654; 15788</t>
+          <t>6530; 15606</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6820; 16547</t>
+          <t>7369; 17373</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17186; 27449</t>
+          <t>16892; 27045</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9718; 19076</t>
+          <t>9243; 18956</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15888; 27060</t>
+          <t>15940; 27519</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14900; 25525</t>
+          <t>14798; 25067</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18867; 31233</t>
+          <t>18360; 31003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25851; 40907</t>
+          <t>25625; 40657</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34538; 49300</t>
+          <t>35061; 49441</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19715; 31205</t>
+          <t>18894; 30538</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7926; 18494</t>
+          <t>7678; 18256</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17057; 28307</t>
+          <t>16841; 28136</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19016; 30523</t>
+          <t>18528; 30202</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8269; 19583</t>
+          <t>8941; 19925</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22615; 35685</t>
+          <t>22732; 35854</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41991; 57976</t>
+          <t>42562; 58265</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18241; 34234</t>
+          <t>18896; 34020</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>43042; 59632</t>
+          <t>43353; 59969</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45728; 63150</t>
+          <t>44571; 63074</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26355; 42930</t>
+          <t>26060; 42557</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50332; 68322</t>
+          <t>50775; 69134</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43274; 60078</t>
+          <t>43274; 61242</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25576; 42119</t>
+          <t>25727; 43065</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49281; 68946</t>
+          <t>51123; 69561</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93675; 117858</t>
+          <t>93496; 119450</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>57120; 80009</t>
+          <t>56307; 79295</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>107825; 133351</t>
+          <t>107372; 132817</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>29059; 45253</t>
+          <t>29671; 47010</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67589; 87219</t>
+          <t>68235; 87185</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>57047; 75788</t>
+          <t>56112; 75357</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30641; 47587</t>
+          <t>31272; 49113</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>60462; 80565</t>
+          <t>60741; 81404</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>62358; 83246</t>
+          <t>63110; 82749</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>64544; 89279</t>
+          <t>65555; 90449</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>134342; 161892</t>
+          <t>133314; 161839</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>125981; 152271</t>
+          <t>126146; 153702</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>204283; 241902</t>
+          <t>203162; 242286</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>205233; 246614</t>
+          <t>204560; 244649</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>258655; 300004</t>
+          <t>259939; 298730</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>221272; 262514</t>
+          <t>220854; 261072</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>228621; 267905</t>
+          <t>228526; 269667</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>285822; 328199</t>
+          <t>284906; 329572</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>436116; 490173</t>
+          <t>438107; 491761</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>445925; 503374</t>
+          <t>443391; 498740</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>556494; 617007</t>
+          <t>559183; 616350</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Provincia-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38,22%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46,3%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42,63%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>26,84%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>39,93%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>31,04%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,19; 39,09</t>
+          <t>26,5; 48,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,17; 51,24</t>
+          <t>36,03; 56,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,92; 41,91</t>
+          <t>32,0; 55,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,0; 49,82</t>
+          <t>17,1; 38,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,63; 57,09</t>
+          <t>29,17; 50,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,38; 53,83</t>
+          <t>21,8; 43,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,38; 40,78</t>
+          <t>25,73; 42,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,38; 51,29</t>
+          <t>34,95; 51,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,71; 45,44</t>
+          <t>29,88; 46,13</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39,44%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37,27%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>38,77%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>32,88%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>48,43%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>39,44%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,27%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>46,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,18; 48,33</t>
+          <t>31,16; 46,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,41; 41,35</t>
+          <t>29,58; 45,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,84; 56,5</t>
+          <t>37,32; 53,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,02; 48,77</t>
+          <t>31,33; 47,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,28; 45,72</t>
+          <t>24,56; 41,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,09; 54,46</t>
+          <t>39,89; 56,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,69; 45,62</t>
+          <t>33,34; 44,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,95; 41,02</t>
+          <t>29,36; 40,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,57; 53,05</t>
+          <t>41,31; 52,88</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>39,42%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30,1%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>48,74%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>14,68%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>40,8%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39,42%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>43,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,11; 58,98</t>
+          <t>30,59; 48,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,52; 22,9</t>
+          <t>21,67; 39,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,72; 52,25</t>
+          <t>33,97; 54,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,01; 48,8</t>
+          <t>37,91; 59,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,85; 39,38</t>
+          <t>8,5; 24,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,39; 53,99</t>
+          <t>30,03; 52,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,36; 51,48</t>
+          <t>36,86; 51,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,88; 28,9</t>
+          <t>16,81; 29,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,24; 49,44</t>
+          <t>34,23; 50,17</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34,08%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>26,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>42,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>35,52%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>32,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,88; 36,7</t>
+          <t>27,89; 46,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,19; 52,55</t>
+          <t>23,42; 41,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,86; 45,63</t>
+          <t>25,07; 43,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,46; 45,28</t>
+          <t>18,99; 36,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,68; 42,25</t>
+          <t>32,5; 51,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,72; 44,12</t>
+          <t>25,55; 45,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,18; 38,42</t>
+          <t>25,83; 37,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,84; 44,31</t>
+          <t>30,09; 43,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,46; 41,83</t>
+          <t>28,62; 42,0</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40,03%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>48,51%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>50,08%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>31,82%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>26,78%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>57,66%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40,03%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>48,51%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>50,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,22; 45,93</t>
+          <t>28,02; 54,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,61; 41,52</t>
+          <t>34,51; 60,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,69; 69,95</t>
+          <t>37,17; 61,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,39; 54,12</t>
+          <t>18,81; 44,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,76; 61,74</t>
+          <t>15,76; 39,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,98; 62,64</t>
+          <t>44,91; 70,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,61; 44,93</t>
+          <t>26,12; 46,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,66; 47,05</t>
+          <t>29,8; 47,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,56; 62,84</t>
+          <t>45,92; 63,27</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45,94%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24,61%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>54,02%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>48,15%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>24,35%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>46,49%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24,61%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>54,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36,27; 58,63</t>
+          <t>35,67; 56,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,08; 35,86</t>
+          <t>15,35; 35,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,56; 57,75</t>
+          <t>42,58; 66,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,27; 55,87</t>
+          <t>36,17; 58,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,12; 35,92</t>
+          <t>15,3; 35,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,9; 66,08</t>
+          <t>34,76; 57,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,1; 54,89</t>
+          <t>38,9; 54,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,76; 31,98</t>
+          <t>18,18; 31,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42,1; 58,23</t>
+          <t>41,59; 57,96</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>43,87%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46,44%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>45,46%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>28,71%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>47,41%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>43,87%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>26,16%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,43; 52,97</t>
+          <t>36,61; 51,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,19; 36,23</t>
+          <t>20,63; 32,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,26; 54,81</t>
+          <t>39,53; 52,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,28; 51,35</t>
+          <t>37,74; 52,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,91; 33,32</t>
+          <t>22,34; 35,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,75; 54,09</t>
+          <t>39,94; 54,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,23; 50,12</t>
+          <t>39,26; 49,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,82; 32,14</t>
+          <t>22,56; 32,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,15; 52,14</t>
+          <t>41,96; 51,76</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29,34%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>45,81%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>47,66%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>26,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>52,84%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>46,77%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>45,81%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>47,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,81; 32,97</t>
+          <t>23,85; 35,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46,44; 59,34</t>
+          <t>39,4; 52,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,85; 53,52</t>
+          <t>40,74; 53,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,0; 36,11</t>
+          <t>20,87; 32,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,25; 52,6</t>
+          <t>46,19; 59,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,93; 53,66</t>
+          <t>39,91; 53,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,53; 32,47</t>
+          <t>23,98; 32,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,19; 53,65</t>
+          <t>44,7; 54,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,76; 52,1</t>
+          <t>42,81; 52,15</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>38,21%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>36,34%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>36,34%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>35,51%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>44,83%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>45,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33,1; 39,48</t>
+          <t>35,15; 41,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32,37; 38,71</t>
+          <t>33,42; 39,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41,77; 48,0</t>
+          <t>42,36; 48,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34,95; 41,31</t>
+          <t>33,18; 39,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,46; 39,48</t>
+          <t>32,33; 39,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,2; 48,82</t>
+          <t>41,9; 48,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,17; 39,48</t>
+          <t>35,16; 39,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>33,72; 37,93</t>
+          <t>33,89; 38,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>43,1; 47,51</t>
+          <t>43,07; 47,32</t>
         </is>
       </c>
     </row>
@@ -1654,20 +1654,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20382</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27340</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24339</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>12137</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>21371</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>14904</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20382</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>27340</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24339</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8225; 17675</t>
+          <t>14129; 26058</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15611; 27428</t>
+          <t>21275; 33622</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10044; 20124</t>
+          <t>18273; 31874</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14932; 26566</t>
+          <t>7734; 17361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21038; 33712</t>
+          <t>15611; 27162</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17915; 30735</t>
+          <t>10468; 20971</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25014; 40185</t>
+          <t>25359; 41714</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39827; 57741</t>
+          <t>39344; 58062</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31226; 47764</t>
+          <t>31407; 48489</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>69</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37733</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36731</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48675</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>34439</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>29261</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>46523</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37733</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36731</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>48675</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27691; 42925</t>
+          <t>29811; 44732</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22614; 36803</t>
+          <t>29151; 45330</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38268; 54274</t>
+          <t>39450; 56401</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30632; 46654</t>
+          <t>27830; 42262</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28857; 45059</t>
+          <t>21863; 36688</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41326; 57576</t>
+          <t>38314; 54513</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62158; 84152</t>
+          <t>61503; 82786</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56175; 76943</t>
+          <t>55077; 76863</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83887; 107038</t>
+          <t>83359; 106699</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25991</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20213</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25461</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>30208</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>9193</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>22915</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25991</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20213</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25461</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23620; 36555</t>
+          <t>20165; 32194</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4711; 14342</t>
+          <t>14550; 26356</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16694; 29347</t>
+          <t>19985; 31853</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19787; 32172</t>
+          <t>23494; 36668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14673; 26447</t>
+          <t>5325; 15302</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19641; 31759</t>
+          <t>16867; 29267</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47785; 65838</t>
+          <t>47148; 65306</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21904; 37518</t>
+          <t>21819; 38266</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39372; 56848</t>
+          <t>39364; 57685</t>
         </is>
       </c>
     </row>
@@ -2244,27 +2244,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26292</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23963</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26017</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>18796</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>29617</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>24096</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26292</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23963</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26017</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13922; 25704</t>
+          <t>20267; 33899</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23131; 36621</t>
+          <t>17382; 31115</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17541; 30950</t>
+          <t>19135; 33508</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19956; 32908</t>
+          <t>13297; 25614</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17576; 31364</t>
+          <t>22650; 36219</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19635; 33678</t>
+          <t>17329; 30635</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37365; 54834</t>
+          <t>36864; 53899</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44379; 63778</t>
+          <t>43302; 63120</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41030; 60310</t>
+          <t>41262; 60555</t>
         </is>
       </c>
     </row>
@@ -2407,32 +2407,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>14018</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21622</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20042</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>10813</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>11205</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>22293</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14018</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>21622</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20042</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6530; 15606</t>
+          <t>9815; 18977</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7369; 17373</t>
+          <t>15384; 27143</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16892; 27045</t>
+          <t>14876; 24681</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9243; 18956</t>
+          <t>6391; 15122</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15940; 27519</t>
+          <t>6593; 16544</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14798; 25067</t>
+          <t>17363; 27097</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18360; 31003</t>
+          <t>18022; 32061</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25625; 40657</t>
+          <t>25751; 40759</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35061; 49441</t>
+          <t>36128; 49780</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>24833</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13652</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>29310</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>25080</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>12398</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>22649</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>24833</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>13652</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>29310</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18894; 30538</t>
+          <t>19284; 30623</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7678; 18256</t>
+          <t>8513; 19539</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16841; 28136</t>
+          <t>23103; 36134</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18528; 30202</t>
+          <t>18842; 30373</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8941; 19925</t>
+          <t>7790; 17879</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22732; 35854</t>
+          <t>16936; 28054</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42562; 58265</t>
+          <t>41289; 58288</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18896; 34020</t>
+          <t>19346; 33279</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>43353; 59969</t>
+          <t>42829; 59685</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>52326</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>33816</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>59725</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>54135</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>33721</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>59803</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>52326</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>33816</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>59725</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44571; 63074</t>
+          <t>43672; 61063</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26060; 42557</t>
+          <t>26665; 42219</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50775; 69134</t>
+          <t>50833; 68147</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43274; 61242</t>
+          <t>44934; 62657</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25727; 43065</t>
+          <t>26237; 42119</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51123; 69561</t>
+          <t>50380; 68913</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93496; 119450</t>
+          <t>93569; 118564</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>56307; 79295</t>
+          <t>55669; 79065</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>107372; 132817</t>
+          <t>106898; 131853</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>102</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>39896</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>70891</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>73493</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>37458</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>77633</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>65852</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>39896</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>70891</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>73493</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>29671; 47010</t>
+          <t>32435; 48888</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>68235; 87185</t>
+          <t>60975; 80605</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>56112; 75357</t>
+          <t>62817; 82912</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>31272; 49113</t>
+          <t>29752; 46434</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>60741; 81404</t>
+          <t>67856; 87702</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>63110; 82749</t>
+          <t>56195; 75293</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65555; 90449</t>
+          <t>66794; 90418</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>133314; 161839</t>
+          <t>134855; 163422</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>126146; 153702</t>
+          <t>126287; 153843</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>317</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>412</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>223065</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>224398</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>279034</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>241471</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>248229</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>307063</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>203162; 242286</t>
+          <t>222136; 262108</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>204560; 244649</t>
+          <t>228270; 270779</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>259939; 298730</t>
+          <t>285940; 329699</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>220854; 261072</t>
+          <t>203647; 241490</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>228526; 269667</t>
+          <t>204349; 246544</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>284906; 329572</t>
+          <t>260763; 300181</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>438107; 491761</t>
+          <t>438009; 492547</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>443391; 498740</t>
+          <t>445637; 501424</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>559183; 616350</t>
+          <t>558745; 613965</t>
         </is>
       </c>
     </row>
